--- a/DeskTop_Version/data/sample_data.xlsx
+++ b/DeskTop_Version/data/sample_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\attensync\salarySync\DeskTop_Version\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D631882-5FAC-408E-B796-B23E0AC87143}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9800C479-6327-4228-B599-737330DBF244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet_List" sheetId="16" r:id="rId1"/>
@@ -166,21 +166,25 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -191,6 +195,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -509,11 +514,11 @@
     <xf numFmtId="18" fontId="1" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -737,7 +742,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="62" t="s">
         <v>30</v>
       </c>
     </row>
@@ -851,7 +856,7 @@
       <c r="F1" s="3"/>
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="63" t="s">
         <v>22</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -869,7 +874,7 @@
       <c r="F2" s="5"/>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="63"/>
+      <c r="A3" s="64"/>
       <c r="B3" s="6">
         <v>0.45833333333333331</v>
       </c>
@@ -3265,7 +3270,7 @@
       <c r="F1" s="3"/>
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="63" t="s">
         <v>23</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -3283,7 +3288,7 @@
       <c r="F2" s="5"/>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="63"/>
+      <c r="A3" s="64"/>
       <c r="B3" s="6">
         <v>0.4375</v>
       </c>
@@ -5674,7 +5679,7 @@
       <c r="F1" s="3"/>
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="63" t="s">
         <v>25</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -5692,7 +5697,7 @@
       <c r="F2" s="5"/>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="63"/>
+      <c r="A3" s="64"/>
       <c r="B3" s="6">
         <v>0.4375</v>
       </c>
@@ -8082,7 +8087,7 @@
       <c r="F1" s="3"/>
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="63" t="s">
         <v>26</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -8100,7 +8105,7 @@
       <c r="F2" s="5"/>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="63"/>
+      <c r="A3" s="64"/>
       <c r="B3" s="6">
         <v>0.4375</v>
       </c>
@@ -10490,7 +10495,7 @@
       <c r="F1" s="3"/>
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="63" t="s">
         <v>27</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -10508,7 +10513,7 @@
       <c r="F2" s="5"/>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="63"/>
+      <c r="A3" s="64"/>
       <c r="B3" s="6">
         <v>0.52083333333333337</v>
       </c>
@@ -12888,7 +12893,7 @@
       <c r="F1" s="3"/>
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="63" t="s">
         <v>28</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -12906,7 +12911,7 @@
       <c r="F2" s="5"/>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="63"/>
+      <c r="A3" s="64"/>
       <c r="B3" s="6">
         <v>0.45833333333333331</v>
       </c>
@@ -15242,7 +15247,7 @@
       <c r="F1" s="3"/>
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="63" t="s">
         <v>29</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -15260,7 +15265,7 @@
       <c r="F2" s="5"/>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="63"/>
+      <c r="A3" s="64"/>
       <c r="B3" s="6">
         <v>0.45833333333333331</v>
       </c>
@@ -17594,7 +17599,7 @@
       <c r="F1" s="3"/>
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="63" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -17612,7 +17617,7 @@
       <c r="F2" s="5"/>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="63"/>
+      <c r="A3" s="64"/>
       <c r="B3" s="6">
         <v>0.4375</v>
       </c>
@@ -20006,7 +20011,7 @@
       <c r="F1" s="3"/>
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="63" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -20024,7 +20029,7 @@
       <c r="F2" s="5"/>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="63"/>
+      <c r="A3" s="64"/>
       <c r="B3" s="6">
         <v>0.4375</v>
       </c>
@@ -22411,7 +22416,7 @@
       <c r="F1" s="3"/>
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="63" t="s">
         <v>14</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -22429,7 +22434,7 @@
       <c r="F2" s="5"/>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="63"/>
+      <c r="A3" s="64"/>
       <c r="B3" s="6">
         <v>0.4375</v>
       </c>
@@ -24812,7 +24817,7 @@
       <c r="F1" s="3"/>
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="63" t="s">
         <v>15</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -24830,7 +24835,7 @@
       <c r="F2" s="5"/>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="63"/>
+      <c r="A3" s="64"/>
       <c r="B3" s="6">
         <v>0.4375</v>
       </c>
@@ -27218,7 +27223,7 @@
       <c r="F1" s="3"/>
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="63" t="s">
         <v>16</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -27236,7 +27241,7 @@
       <c r="F2" s="5"/>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="63"/>
+      <c r="A3" s="64"/>
       <c r="B3" s="6">
         <v>0.4375</v>
       </c>
@@ -29627,7 +29632,7 @@
       <c r="F1" s="3"/>
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="63" t="s">
         <v>17</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -29645,7 +29650,7 @@
       <c r="F2" s="5"/>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="63"/>
+      <c r="A3" s="64"/>
       <c r="B3" s="6">
         <v>0.4375</v>
       </c>
@@ -32036,7 +32041,7 @@
       <c r="F1" s="3"/>
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="63" t="s">
         <v>18</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -32054,7 +32059,7 @@
       <c r="F2" s="5"/>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="63"/>
+      <c r="A3" s="64"/>
       <c r="B3" s="6">
         <v>0.4375</v>
       </c>
@@ -34434,7 +34439,7 @@
       <c r="F1" s="3"/>
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="63" t="s">
         <v>21</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -34452,7 +34457,7 @@
       <c r="F2" s="5"/>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="63"/>
+      <c r="A3" s="64"/>
       <c r="B3" s="6">
         <v>0.45833333333333331</v>
       </c>
